--- a/assets/work/Jill Jones initial overview.slim.xlsx
+++ b/assets/work/Jill Jones initial overview.slim.xlsx
@@ -12,7 +12,8 @@
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Quote" sheetId="1" r:id="rId1"/>
+    <sheet name="Summary" sheetId="3" r:id="rId6"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="189">
   <si>
     <t>*Date of birth 30. Jun, 1989</t>
   </si>
@@ -231,10 +232,10 @@
     <t>148,83 €</t>
   </si>
   <si>
-    <t>330,45 €</t>
-  </si>
-  <si>
-    <t>314,06 €</t>
+    <t>339,79 €</t>
+  </si>
+  <si>
+    <t>318,73 €</t>
   </si>
   <si>
     <t>300 €/year</t>
@@ -285,7 +286,7 @@
     <t>Gothaer / MediVita250</t>
   </si>
   <si>
-    <t>Ref 125/1.155</t>
+    <t>Ref 125/1155</t>
   </si>
   <si>
     <t>577,75 € + 35,47 €</t>
@@ -300,10 +301,10 @@
     <t>191,66 €</t>
   </si>
   <si>
-    <t>713,32 €</t>
-  </si>
-  <si>
-    <t>548,33 €</t>
+    <t>748,79 €</t>
+  </si>
+  <si>
+    <t>566,06 €</t>
   </si>
   <si>
     <t>250 €/year</t>
@@ -339,7 +340,7 @@
     <t>BBKK / GesundheitVARIO 800</t>
   </si>
   <si>
-    <t>Ref 3814/1.138</t>
+    <t>Ref 3814/1138</t>
   </si>
   <si>
     <t>601,23 € + 50,00 €</t>
@@ -354,10 +355,10 @@
     <t>295,70 €</t>
   </si>
   <si>
-    <t>722,07 €</t>
-  </si>
-  <si>
-    <t>656,74 €</t>
+    <t>772,07 €</t>
+  </si>
+  <si>
+    <t>681,74 €</t>
   </si>
   <si>
     <t>800 €/year</t>
@@ -408,10 +409,10 @@
     <t>205,35 €</t>
   </si>
   <si>
-    <t>1.249,11 €</t>
-  </si>
-  <si>
-    <t>829,91 €</t>
+    <t>1.304,11 €</t>
+  </si>
+  <si>
+    <t>857,41 €</t>
   </si>
   <si>
     <t>0 €/year</t>
@@ -451,13 +452,166 @@
   </si>
   <si>
     <t>Dependents can be included cost-free</t>
+  </si>
+  <si>
+    <t>Quote Summary</t>
+  </si>
+  <si>
+    <t>Client name</t>
+  </si>
+  <si>
+    <t>Segment</t>
+  </si>
+  <si>
+    <t>Employee</t>
+  </si>
+  <si>
+    <t>Birth date</t>
+  </si>
+  <si>
+    <t>1994-01-15</t>
+  </si>
+  <si>
+    <t>Buy date</t>
+  </si>
+  <si>
+    <t>2026-06-03</t>
+  </si>
+  <si>
+    <t>Sick cover</t>
+  </si>
+  <si>
+    <t>80.000 €</t>
+  </si>
+  <si>
+    <t>Prior cover</t>
+  </si>
+  <si>
+    <t>No prior cover</t>
+  </si>
+  <si>
+    <t>Exam</t>
+  </si>
+  <si>
+    <t>Exam OK</t>
+  </si>
+  <si>
+    <t>Specialist</t>
+  </si>
+  <si>
+    <t>Not important</t>
+  </si>
+  <si>
+    <t>Vision</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Temp visa</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>No PVN</t>
+  </si>
+  <si>
+    <t>Natural medicine</t>
+  </si>
+  <si>
+    <t>Plan 1</t>
+  </si>
+  <si>
+    <t>Pre-ex total</t>
+  </si>
+  <si>
+    <t>9,34 €</t>
+  </si>
+  <si>
+    <t>Vision correction</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Selected addon</t>
+  </si>
+  <si>
+    <t>Pre-ex</t>
+  </si>
+  <si>
+    <t>Optional note</t>
+  </si>
+  <si>
+    <t>Plan</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Sick</t>
+  </si>
+  <si>
+    <t>43A</t>
+  </si>
+  <si>
+    <t>PVN</t>
+  </si>
+  <si>
+    <t>Plan 2</t>
+  </si>
+  <si>
+    <t>35,47 €</t>
+  </si>
+  <si>
+    <t>5,00 €</t>
+  </si>
+  <si>
+    <t>Hospital</t>
+  </si>
+  <si>
+    <t>Consumer</t>
+  </si>
+  <si>
+    <t>Natural</t>
+  </si>
+  <si>
+    <t>Plan 3</t>
+  </si>
+  <si>
+    <t>50,00 €</t>
+  </si>
+  <si>
+    <t>Plan 4</t>
+  </si>
+  <si>
+    <t>55,00 €</t>
+  </si>
+  <si>
+    <t>Dependants</t>
+  </si>
+  <si>
+    <t>Dependant 1</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Melvin</t>
+  </si>
+  <si>
+    <t>2018-07-01</t>
+  </si>
+  <si>
+    <t>Pre-ex charges</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <fonts count="18">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -587,8 +741,19 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <family val="2"/>
+      <b val="1"/>
+      <color/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <family val="2"/>
+      <b val="1"/>
+      <color/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -627,6 +792,11 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFEEEEEE"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBFDFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -743,7 +913,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
       <alignment wrapText="true"/>
@@ -843,6 +1013,18 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="false">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="false">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="true" applyAlignment="false">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="false">
+      <alignment/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1387,8 +1569,6 @@
     <col customWidth="true" max="8" min="8" width="39.7109375"/>
     <col customWidth="true" max="9" min="9" width="1.7109375"/>
     <col customWidth="true" max="10" min="10" width="39.7109375"/>
-    <col customWidth="true" max="11" min="11" width="1.7109375"/>
-    <col customWidth="true" max="12" min="12" width="39.7109375"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" s="1" customFormat="true" ht="90" customHeight="true">
@@ -1396,7 +1576,6 @@
       <c r="F1" s="2"/>
       <c r="H1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="L1" s="2"/>
     </row>
     <row r="2" spans="1:12" s="1" customFormat="true" ht="60" customHeight="true"/>
     <row r="3" spans="1:12" s="1" customFormat="true" ht="23.25">
@@ -1423,7 +1602,6 @@
       <c r="J4" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="L4" s="4"/>
     </row>
     <row r="5" spans="1:12" s="31" customFormat="true" ht="12.75">
       <c r="A5" s="30"/>
@@ -1456,7 +1634,6 @@
       <c r="J6" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="L6" s="8"/>
     </row>
     <row r="7" spans="1:12" s="1" customFormat="true" ht="23.25">
       <c r="A7" s="9" t="s">
@@ -1474,7 +1651,6 @@
       <c r="J7" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="L7" s="10"/>
     </row>
     <row r="8" spans="1:12" s="1" customFormat="true"/>
     <row r="9" spans="1:12" s="1" customFormat="true">
@@ -2120,4 +2296,599 @@
   <pageSetup horizontalDpi="4294967293" r:id="rId1" orientation="portrait"/>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <cols>
+    <col customWidth="true" max="1" min="1" width="34"/>
+    <col customWidth="true" max="2" min="2" width="40"/>
+    <col customWidth="true" max="3" min="3" width="16"/>
+    <col customWidth="true" max="4" min="4" width="42"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="37" t="s">
+        <v>138</v>
+      </c>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="38" t="s">
+        <v>139</v>
+      </c>
+      <c r="B3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="38" t="s">
+        <v>140</v>
+      </c>
+      <c r="B4" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="38" t="s">
+        <v>142</v>
+      </c>
+      <c r="B5" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="38" t="s">
+        <v>144</v>
+      </c>
+      <c r="B6" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="38" t="s">
+        <v>146</v>
+      </c>
+      <c r="B7" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="38" t="s">
+        <v>148</v>
+      </c>
+      <c r="B8" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="38" t="s">
+        <v>150</v>
+      </c>
+      <c r="B9" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="38" t="s">
+        <v>152</v>
+      </c>
+      <c r="B10" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="38" t="s">
+        <v>154</v>
+      </c>
+      <c r="B11" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="38" t="s">
+        <v>156</v>
+      </c>
+      <c r="B12" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="38" t="s">
+        <v>158</v>
+      </c>
+      <c r="B13" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="38" t="s">
+        <v>159</v>
+      </c>
+      <c r="B14" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="15"/>
+    <row r="16">
+      <c r="A16" s="40" t="s">
+        <v>160</v>
+      </c>
+      <c r="B16" s="40" t="s">
+        <v>56</v>
+      </c>
+      <c r="C16" s="39"/>
+      <c r="D16" s="39"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="40" t="s">
+        <v>161</v>
+      </c>
+      <c r="B17" s="39" t="s">
+        <v>162</v>
+      </c>
+      <c r="C17" s="39"/>
+      <c r="D17" s="39"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="40" t="s">
+        <v>163</v>
+      </c>
+      <c r="B18" s="39" t="s">
+        <v>95</v>
+      </c>
+      <c r="C18" s="39"/>
+      <c r="D18" s="39"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="40" t="s">
+        <v>164</v>
+      </c>
+      <c r="B19" s="40" t="s">
+        <v>165</v>
+      </c>
+      <c r="C19" s="40" t="s">
+        <v>166</v>
+      </c>
+      <c r="D19" s="40" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="39" t="s">
+        <v>168</v>
+      </c>
+      <c r="B20" s="39" t="s">
+        <v>169</v>
+      </c>
+      <c r="C20" s="39" t="s">
+        <v>162</v>
+      </c>
+      <c r="D20" s="39" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="39" t="s">
+        <v>170</v>
+      </c>
+      <c r="B21" s="39" t="s">
+        <v>171</v>
+      </c>
+      <c r="C21" s="39" t="s">
+        <v>95</v>
+      </c>
+      <c r="D21" s="39" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="39" t="s">
+        <v>172</v>
+      </c>
+      <c r="B22" s="39" t="s">
+        <v>172</v>
+      </c>
+      <c r="C22" s="39" t="s">
+        <v>95</v>
+      </c>
+      <c r="D22" s="39" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="23"/>
+    <row r="24">
+      <c r="A24" s="40" t="s">
+        <v>173</v>
+      </c>
+      <c r="B24" s="40" t="s">
+        <v>81</v>
+      </c>
+      <c r="C24" s="39"/>
+      <c r="D24" s="39"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="40" t="s">
+        <v>161</v>
+      </c>
+      <c r="B25" s="39" t="s">
+        <v>174</v>
+      </c>
+      <c r="C25" s="39"/>
+      <c r="D25" s="39"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="40" t="s">
+        <v>163</v>
+      </c>
+      <c r="B26" s="39" t="s">
+        <v>175</v>
+      </c>
+      <c r="C26" s="39"/>
+      <c r="D26" s="39"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="40" t="s">
+        <v>164</v>
+      </c>
+      <c r="B27" s="40" t="s">
+        <v>165</v>
+      </c>
+      <c r="C27" s="40" t="s">
+        <v>166</v>
+      </c>
+      <c r="D27" s="40" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="39" t="s">
+        <v>168</v>
+      </c>
+      <c r="B28" s="39" t="s">
+        <v>169</v>
+      </c>
+      <c r="C28" s="39" t="s">
+        <v>174</v>
+      </c>
+      <c r="D28" s="39" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="39" t="s">
+        <v>170</v>
+      </c>
+      <c r="B29" s="39" t="s">
+        <v>171</v>
+      </c>
+      <c r="C29" s="39" t="s">
+        <v>95</v>
+      </c>
+      <c r="D29" s="39" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="39" t="s">
+        <v>172</v>
+      </c>
+      <c r="B30" s="39" t="s">
+        <v>172</v>
+      </c>
+      <c r="C30" s="39" t="s">
+        <v>95</v>
+      </c>
+      <c r="D30" s="39" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="39" t="s">
+        <v>176</v>
+      </c>
+      <c r="B31" s="39" t="s">
+        <v>169</v>
+      </c>
+      <c r="C31" s="39" t="s">
+        <v>95</v>
+      </c>
+      <c r="D31" s="39" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="39" t="s">
+        <v>50</v>
+      </c>
+      <c r="B32" s="39" t="s">
+        <v>169</v>
+      </c>
+      <c r="C32" s="39" t="s">
+        <v>95</v>
+      </c>
+      <c r="D32" s="39" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="39" t="s">
+        <v>177</v>
+      </c>
+      <c r="B33" s="39" t="s">
+        <v>177</v>
+      </c>
+      <c r="C33" s="39" t="s">
+        <v>95</v>
+      </c>
+      <c r="D33" s="39" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="39" t="s">
+        <v>178</v>
+      </c>
+      <c r="B34" s="39" t="s">
+        <v>178</v>
+      </c>
+      <c r="C34" s="39" t="s">
+        <v>95</v>
+      </c>
+      <c r="D34" s="39" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="35"/>
+    <row r="36">
+      <c r="A36" s="40" t="s">
+        <v>179</v>
+      </c>
+      <c r="B36" s="40" t="s">
+        <v>99</v>
+      </c>
+      <c r="C36" s="39"/>
+      <c r="D36" s="39"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="40" t="s">
+        <v>161</v>
+      </c>
+      <c r="B37" s="39" t="s">
+        <v>180</v>
+      </c>
+      <c r="C37" s="39"/>
+      <c r="D37" s="39"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="40" t="s">
+        <v>163</v>
+      </c>
+      <c r="B38" s="39" t="s">
+        <v>95</v>
+      </c>
+      <c r="C38" s="39"/>
+      <c r="D38" s="39"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="40" t="s">
+        <v>164</v>
+      </c>
+      <c r="B39" s="40" t="s">
+        <v>165</v>
+      </c>
+      <c r="C39" s="40" t="s">
+        <v>166</v>
+      </c>
+      <c r="D39" s="40" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="39" t="s">
+        <v>168</v>
+      </c>
+      <c r="B40" s="39" t="s">
+        <v>169</v>
+      </c>
+      <c r="C40" s="39" t="s">
+        <v>180</v>
+      </c>
+      <c r="D40" s="39" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="39" t="s">
+        <v>170</v>
+      </c>
+      <c r="B41" s="39" t="s">
+        <v>171</v>
+      </c>
+      <c r="C41" s="39" t="s">
+        <v>95</v>
+      </c>
+      <c r="D41" s="39" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="39" t="s">
+        <v>172</v>
+      </c>
+      <c r="B42" s="39" t="s">
+        <v>172</v>
+      </c>
+      <c r="C42" s="39" t="s">
+        <v>95</v>
+      </c>
+      <c r="D42" s="39" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="39" t="s">
+        <v>176</v>
+      </c>
+      <c r="B43" s="39" t="s">
+        <v>169</v>
+      </c>
+      <c r="C43" s="39" t="s">
+        <v>95</v>
+      </c>
+      <c r="D43" s="39" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="39" t="s">
+        <v>50</v>
+      </c>
+      <c r="B44" s="39" t="s">
+        <v>169</v>
+      </c>
+      <c r="C44" s="39" t="s">
+        <v>95</v>
+      </c>
+      <c r="D44" s="39" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="39" t="s">
+        <v>177</v>
+      </c>
+      <c r="B45" s="39" t="s">
+        <v>177</v>
+      </c>
+      <c r="C45" s="39" t="s">
+        <v>95</v>
+      </c>
+      <c r="D45" s="39" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="46"/>
+    <row r="47">
+      <c r="A47" s="40" t="s">
+        <v>181</v>
+      </c>
+      <c r="B47" s="40" t="s">
+        <v>116</v>
+      </c>
+      <c r="C47" s="39"/>
+      <c r="D47" s="39"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="40" t="s">
+        <v>161</v>
+      </c>
+      <c r="B48" s="39" t="s">
+        <v>182</v>
+      </c>
+      <c r="C48" s="39"/>
+      <c r="D48" s="39"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="40" t="s">
+        <v>163</v>
+      </c>
+      <c r="B49" s="39" t="s">
+        <v>95</v>
+      </c>
+      <c r="C49" s="39"/>
+      <c r="D49" s="39"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="40" t="s">
+        <v>164</v>
+      </c>
+      <c r="B50" s="40" t="s">
+        <v>165</v>
+      </c>
+      <c r="C50" s="40" t="s">
+        <v>166</v>
+      </c>
+      <c r="D50" s="40" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="39" t="s">
+        <v>168</v>
+      </c>
+      <c r="B51" s="39" t="s">
+        <v>169</v>
+      </c>
+      <c r="C51" s="39" t="s">
+        <v>95</v>
+      </c>
+      <c r="D51" s="39" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="39" t="s">
+        <v>172</v>
+      </c>
+      <c r="B52" s="39" t="s">
+        <v>172</v>
+      </c>
+      <c r="C52" s="39" t="s">
+        <v>182</v>
+      </c>
+      <c r="D52" s="39" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="53"/>
+    <row r="54">
+      <c r="A54" s="38" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="55"/>
+    <row r="56">
+      <c r="A56" s="38" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="38" t="s">
+        <v>185</v>
+      </c>
+      <c r="B57" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="38" t="s">
+        <v>142</v>
+      </c>
+      <c r="B58" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="38" t="s">
+        <v>154</v>
+      </c>
+      <c r="B59" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="38" t="s">
+        <v>188</v>
+      </c>
+      <c r="B60" t="s">
+        <v>95</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
 </file>